--- a/out/LSTM-mamba2_repeat_4_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.854026995542006</v>
+        <v>7.399999562500023</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.961239300729744</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.561239300729744</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.961239300729744</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.961239300729744</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.961239300729744</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.961239300729744</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-5.470734959421679e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.0235552892915402</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001787741328692064</v>
+        <v>0.04717365639325231</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3611519977329477</v>
+        <v>0.09100653982477747</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7229377694205681</v>
+        <v>0.2056931264248386</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1007045420590343</v>
+        <v>0.02799463081832791</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5626678737471504</v>
+        <v>0.1705589847875484</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01241288820161953</v>
+        <v>0.005678873425097509</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4865895292528835</v>
+        <v>0.153879958549737</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01569118945727869</v>
+        <v>0.004917092903700887</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5055306774015966</v>
+        <v>0.1580298336115703</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.007595996166627018</v>
+        <v>0.002400960930096784</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5050025181514221</v>
+        <v>0.157910286646544</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003546144155583912</v>
+        <v>0.001143586999493277</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5044865606853215</v>
+        <v>0.1577932609992251</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00133364335817116</v>
+        <v>0.000473214064411936</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5036015774377952</v>
+        <v>0.1575953407944017</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001085645801577065</v>
+        <v>0.0003268187407112325</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5044374649366269</v>
+        <v>0.1577747739985299</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004154861237540181</v>
+        <v>0.0001335217100878401</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5041810196816998</v>
+        <v>0.1577146379686887</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002169465097239945</v>
+        <v>6.649436238847041e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5041987924541277</v>
+        <v>0.1577146294899893</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.086291132104018e-05</v>
+        <v>2.334266066831255e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5041230430250282</v>
+        <v>0.1576940673623667</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.896188643945796e-05</v>
+        <v>1.0461098056069e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5041296502390507</v>
+        <v>0.1576916152873959</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.631658308627986e-05</v>
+        <v>2.340732518447637e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5041235919599847</v>
+        <v>0.1576863834801766</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.8457880197075e-06</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5041165767594467</v>
+        <v>0.1576809284348937</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-1.310715457649435e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.50410933554971</v>
+        <v>0.1576754228010664</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.414534976498284e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5041035615707732</v>
+        <v>0.1576702293063323</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.589420887334386e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5040977924279056</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.130804869371821e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649015120096</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649812229541</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649732518597</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576651326737488</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576653877487716</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576651406448432</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.157665100789371</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576651406448432</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576652362979769</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.157665172529221</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576651326737488</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576648616565373</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576647819455925</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576648297721592</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649493385763</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649333963874</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1576649493385763</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5037080129473598</v>
+        <v>0.1576649333963874</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.001907714694896033</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5638413682996137</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5638357930891318</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="88">
@@ -70893,21 +70893,21 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.05701860110942733</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5626287535412013</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5622241275397111</v>
+        <v>0.1576651406448432</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.09392419454810236</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7508214653530488</v>
+        <v>0.1576653558643938</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.02770569227130949</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7119053798360965</v>
+        <v>0.1576652681823547</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7011568355292754</v>
+        <v>0.157665220355788</v>
       </c>
     </row>
     <row r="93">
@@ -74868,21 +74868,21 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.0489266444422875</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7325513765484546</v>
+        <v>0.1576652681823547</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7320955995111438</v>
+        <v>0.157665084847182</v>
       </c>
     </row>
     <row r="95">
@@ -76458,21 +76458,21 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>4.195984922153427e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7404986906256537</v>
+        <v>0.1576650928182765</v>
       </c>
     </row>
     <row r="96">
@@ -77253,21 +77253,21 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>1.02881444368925e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7488915012716553</v>
+        <v>0.157665100789371</v>
       </c>
     </row>
     <row r="97">
@@ -78048,21 +78048,21 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>1.780205024512575e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7572761466806608</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.757270536837948</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="99">
@@ -79638,21 +79638,21 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0.06573053538935469</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7978528112373897</v>
+        <v>0.1576651486159377</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7978528112373897</v>
+        <v>0.1576652123846936</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7978528112373897</v>
+        <v>0.1576653239800159</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7974849868840312</v>
+        <v>0.1576653718065827</v>
       </c>
     </row>
     <row r="103">
@@ -82818,21 +82818,21 @@
         <v>0</v>
       </c>
       <c r="IY103" t="n">
-        <v>-0.02653856938049827</v>
+        <v>0</v>
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1576653319511104</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1576652602112603</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1576653797776771</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.770946417503533</v>
+        <v>0.157665220355788</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7704601988416496</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>0.0006844377638328265</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8134651858145352</v>
+        <v>0.1576649732518597</v>
       </c>
     </row>
     <row r="110">
@@ -88383,7 +88383,7 @@
         <v>0</v>
       </c>
       <c r="IY110" t="n">
-        <v>0.06266825379476806</v>
+        <v>0</v>
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8972937620403976</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="111">
@@ -89178,7 +89178,7 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>0.03133412689738403</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8968875009442747</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8700398191398893</v>
+        <v>0.1576649573096708</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-0.164683141520787</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7000665970113289</v>
+        <v>0.1576648377432537</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6995918731843126</v>
+        <v>0.1576647978877814</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.1171425773404531</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9347663042179575</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.114225018217301</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.045712659832669</v>
+        <v>0.1576650768760876</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.05383863360699806</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.038896166814836</v>
+        <v>0.1576650609338987</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.02446413327059966</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.033852264922288</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.0101859712804107</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.029694052442835</v>
+        <v>0.157664997165143</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.002433014356829137</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.024340272013733</v>
+        <v>0.1576648935409151</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.02084234450582</v>
+        <v>0.157664773974498</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.09211540360670678</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.206474683929051</v>
+        <v>0.1576648935409151</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.06467162599335323</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.243337217791902</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.05094986790042878</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.280382480041021</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="125">
@@ -100308,7 +100308,7 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>0.0138411304644788</v>
+        <v>0</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.256978235096012</v>
+        <v>0.1576649174541985</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.0146168586488533</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.257703490087851</v>
+        <v>0.1576649254252929</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809758</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.961239300729744</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.961239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.961239300729744</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809758</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-6.225535188009962e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.02680523992783321</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.961239300729744</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001787741328692064</v>
+        <v>0.05368223092482775</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3611519977329477</v>
+        <v>0.1035628178797698</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.961239300729744</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7229377694205681</v>
+        <v>0.2340726173859527</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1007045420590343</v>
+        <v>0.03185701233491891</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.4621290720809758</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5626678737471504</v>
+        <v>0.1940910655384047</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01241288820161953</v>
+        <v>0.006463098305991391</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4865895292528835</v>
+        <v>0.1751115462782285</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01569118945727869</v>
+        <v>0.005595804768822115</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5055306774015966</v>
+        <v>0.1798346437410866</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.007595996166627018</v>
+        <v>0.002733469350753161</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5050025181514221</v>
+        <v>0.1796992843109614</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003546144155583912</v>
+        <v>0.001301943671325683</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5044865606853215</v>
+        <v>0.1795668135918481</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00133364335817116</v>
+        <v>0.0005394625785737758</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5036015774377952</v>
+        <v>0.1793422945929053</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001085645801577065</v>
+        <v>0.0003723473586227737</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5044374649366269</v>
+        <v>0.1795470337482973</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004154861237540181</v>
+        <v>0.0001522060337741069</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5041810196816998</v>
+        <v>0.1794793332280822</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002169465097239945</v>
+        <v>7.651693655507841e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5041987924541277</v>
+        <v>0.1794800211430304</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.086291132104018e-05</v>
+        <v>2.701670927346418e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5041230430250282</v>
+        <v>0.1794572982228673</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.896188643945796e-05</v>
+        <v>1.275163110141255e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5041296502390507</v>
+        <v>0.1794552236182713</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.631658308627986e-05</v>
+        <v>3.470075982824195e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5041235919599847</v>
+        <v>0.179449957374725</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.8457880197075e-06</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5041165767594467</v>
+        <v>0.179444437322973</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-1.310715457649435e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.50410933554971</v>
+        <v>0.1794388587976701</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.414534976498284e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5041035615707732</v>
+        <v>0.179433665302936</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.589420887334386e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5040977924279056</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.130804869371821e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794283375086133</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794283773640855</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794284172195578</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794284092484633</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285686703525</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794288237453753</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285766414469</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285367859746</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285447570691</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285766414469</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794286722945806</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794286085258247</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285686703525</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794285447570691</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.179428297653141</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794282179421962</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794282657687629</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.17942838533518</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.1794283693929911</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.2621290720809757</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5040922471261243</v>
+        <v>0.17942838533518</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5037080129473598</v>
+        <v>0.1794283693929911</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.001907714694896033</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5638413682996137</v>
+        <v>0.1794284251906522</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.561239300729744</v>
+        <v>0.3813603670668531</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5638357930891318</v>
+        <v>0.1794284251906522</v>
       </c>
     </row>
     <row r="88">
@@ -70893,21 +70893,21 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.05701860110942733</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.254026995542006</v>
+        <v>0.3813603670668531</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5626287535412013</v>
+        <v>0.1794284251906522</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5622241275397111</v>
+        <v>0.1794285766414469</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.09392419454810236</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7508214653530488</v>
+        <v>0.1794287918609974</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.02770569227130949</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809758</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7119053798360965</v>
+        <v>0.1794287041789584</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.4621290720809758</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7011568355292754</v>
+        <v>0.1794286563523917</v>
       </c>
     </row>
     <row r="93">
@@ -74868,21 +74868,21 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.0489266444422875</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.1813603670668529</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7325513765484546</v>
+        <v>0.1794287041789584</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.561239300729744</v>
+        <v>0.1813603670668529</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7320955995111438</v>
+        <v>0.1794285208437857</v>
       </c>
     </row>
     <row r="95">
@@ -76458,21 +76458,21 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>4.195984922153427e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7404986906256537</v>
+        <v>0.1794285288148802</v>
       </c>
     </row>
     <row r="96">
@@ -77253,21 +77253,21 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>1.02881444368925e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7488915012716553</v>
+        <v>0.1794285367859746</v>
       </c>
     </row>
     <row r="97">
@@ -78048,21 +78048,21 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>1.780205024512575e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7572761466806608</v>
+        <v>0.1794285447570691</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.561239300729744</v>
+        <v>0.3813603670668529</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.757270536837948</v>
+        <v>0.1794285447570691</v>
       </c>
     </row>
     <row r="99">
@@ -79638,21 +79638,21 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0.06573053538935469</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809758</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7978528112373897</v>
+        <v>0.1794285846125414</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7978528112373897</v>
+        <v>0.1794286483812972</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.462129072080976</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7978528112373897</v>
+        <v>0.1794287599766196</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.961239300729744</v>
+        <v>-0.462129072080976</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7974849868840312</v>
+        <v>0.1794288078031863</v>
       </c>
     </row>
     <row r="103">
@@ -82818,21 +82818,21 @@
         <v>0</v>
       </c>
       <c r="IY103" t="n">
-        <v>-0.02653856938049827</v>
+        <v>0</v>
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.462129072080976</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1794287679477141</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.770946417503533</v>
+        <v>0.179428696207864</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1794288157742808</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228805</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1794286563523917</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.462129072080976</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.770946417503533</v>
+        <v>0.1794284251906522</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.561239300729744</v>
+        <v>0.3813603670668528</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7704601988416496</v>
+        <v>0.1794283773640855</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>0.0006844377638328265</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8134651858145352</v>
+        <v>0.1794284092484633</v>
       </c>
     </row>
     <row r="110">
@@ -88383,7 +88383,7 @@
         <v>0</v>
       </c>
       <c r="IY110" t="n">
-        <v>0.06266825379476806</v>
+        <v>0</v>
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8972937620403976</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="111">
@@ -89178,7 +89178,7 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>0.03133412689738403</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8968875009442747</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8700398191398893</v>
+        <v>0.1794283933062744</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-0.164683141520787</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7000665970113289</v>
+        <v>0.1794282737398574</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6995918731843126</v>
+        <v>0.1794282338843851</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.1171425773404531</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9347663042179575</v>
+        <v>0.1794283773640855</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.114225018217301</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.045712659832669</v>
+        <v>0.1794285128726913</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.05383863360699806</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.961239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.038896166814836</v>
+        <v>0.1794284969305024</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.02446413327059966</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.033852264922288</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.0101859712804107</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.029694052442835</v>
+        <v>0.1794284331617467</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.002433014356829137</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.024340272013733</v>
+        <v>0.1794283295375188</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.02084234450582</v>
+        <v>0.1794282099711017</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.09211540360670678</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.206474683929051</v>
+        <v>0.1794283295375188</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.06467162599335323</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.243337217791902</v>
+        <v>0.1794283773640855</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.05094986790042878</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.280382480041021</v>
+        <v>0.179428473017219</v>
       </c>
     </row>
     <row r="125">
@@ -100308,7 +100308,7 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>0.0138411304644788</v>
+        <v>0</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.256978235096012</v>
+        <v>0.1794283534508022</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.0146168586488533</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.961239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.257703490087851</v>
+        <v>0.1794283614218966</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2367796897888184</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.09729613363742828</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4621290720809758</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.008137082681059837</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.05121350660920143</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.05715209618210793</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.04487625136971474</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.04592419415712357</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.024849806214682</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.04084154963493347</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.03030999004840851</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.02624035067856312</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.02064593695104122</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.02175143361091614</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01960419304668903</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01168414391577244</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.008586348965764046</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006983090192079544</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01310867816209793</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01411594450473785</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01289616338908672</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01465598121285439</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01559755578637123</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01348416693508625</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01308484561741352</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01695701107382774</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.02154658921062946</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.02180591970682144</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.02151179686188698</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.02296889945864677</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01763820648193359</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.005797440186142921</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01851572096347809</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.02027967013418674</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02813242003321648</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.02624510787427425</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.02285559475421906</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0154474563896656</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01108015887439251</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01034678425639868</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002283345907926559</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.008153846487402916</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.009420963004231453</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.01950285956263542</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4621290720809758</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-6.225535188009962e-05</v>
+        <v>-4.119370989268645e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.02680523992783321</v>
+        <v>0.01773681546523015</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001675825566053391</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.05368223092482775</v>
+        <v>0.0355209658014758</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1035628178797698</v>
+        <v>0.06852669831488417</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0229477621614933</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2340726173859527</v>
+        <v>0.1548829045442364</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03185701233491891</v>
+        <v>0.02107919654257601</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.04039856791496277</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4621290720809758</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1940910655384047</v>
+        <v>0.1284278502971099</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.006463098305991391</v>
+        <v>0.00427495792930646</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.08847580850124359</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1751115462782285</v>
+        <v>0.1158677610717299</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.005595804768822115</v>
+        <v>0.003700709508299024</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.1477203816175461</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1798346437410866</v>
+        <v>0.1189911560925993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.002733469350753161</v>
+        <v>0.001806645879281488</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.1665422022342682</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1796992843109614</v>
+        <v>0.1188999003229144</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001301943671325683</v>
+        <v>0.000859614064772717</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.1658974438905716</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1795668135918481</v>
+        <v>0.1188105396499208</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0005394625785737758</v>
+        <v>0.0003551915013673139</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.151442676782608</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1793422945929053</v>
+        <v>0.1186602043405739</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0003723473586227737</v>
+        <v>0.0002450215627684635</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.133261650800705</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1795470337482973</v>
+        <v>0.118794172615312</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001522060337741069</v>
+        <v>9.937449783362837e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.1223225742578506</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1794793332280822</v>
+        <v>0.1187476282579435</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>7.651693655507841e-05</v>
+        <v>4.912190049968322e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.1129581779241562</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1794800211430304</v>
+        <v>0.1187463887836386</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.701670927346418e-05</v>
+        <v>1.59945634580093e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.09455032646656036</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1794572982228673</v>
+        <v>0.1187297178019956</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.275163110141255e-05</v>
+        <v>6.452665226717778e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.08236436545848846</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1794552236182713</v>
+        <v>0.1187266529804359</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.470075982824195e-06</v>
+        <v>6.467173218827975e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.06388219445943832</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.179449957374725</v>
+        <v>0.1187214728277067</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-7.373950752172664e-07</v>
+        <v>-2.335871922010791e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.05363555997610092</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.179444437322973</v>
+        <v>0.1187161159109841</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.155312586922569e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.04489045962691307</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1794388587976701</v>
+        <v>0.1187106820170067</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0338849313557148</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.179433665302936</v>
+        <v>0.118705537443073</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02931174635887146</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01690061017870903</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1794283375086133</v>
+        <v>0.1187002096487503</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01639630645513535</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1794283773640855</v>
+        <v>0.1187002495042225</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.009122107177972794</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1794284172195578</v>
+        <v>0.1187002893596948</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01416838727891445</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1794284092484633</v>
+        <v>0.1187002813886004</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01588008552789688</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1794285686703525</v>
+        <v>0.1187004408104895</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.02292420901358128</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02567678317427635</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1794288237453753</v>
+        <v>0.1187006958855123</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02292145416140556</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1794285766414469</v>
+        <v>0.1187004487815839</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0231353547424078</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1794285367859746</v>
+        <v>0.1187004089261116</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01499915216118097</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01514884643256664</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1794285447570691</v>
+        <v>0.1187004168972061</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01590832322835922</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.04484297707676888</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1794285766414469</v>
+        <v>0.1187004487815839</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.04252204298973083</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.16</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1794286722945806</v>
+        <v>0.1187005444347176</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.03758137673139572</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1794286085258247</v>
+        <v>0.1187004806659617</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.03207309916615486</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1794285686703525</v>
+        <v>0.1187004408104895</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.04073122516274452</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1794285447570691</v>
+        <v>0.1187004168972061</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02916976809501648</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.179428297653141</v>
+        <v>0.118700169793278</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01283202134072781</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1794282179421962</v>
+        <v>0.1187000900823332</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006864962168037891</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1794282657687629</v>
+        <v>0.1187001379088999</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001993326470255852</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.17942838533518</v>
+        <v>0.118700257475317</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003737008199095726</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.105618511228805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1794283693929911</v>
+        <v>0.1187002415331281</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001786178909242153</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2621290720809757</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.17942838533518</v>
+        <v>0.118700257475317</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0002030450850725174</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.381360367066853</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1794283693929911</v>
+        <v>0.1187002415331281</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.003608384169638157</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1794284251906522</v>
+        <v>0.1187002973307893</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01283827051520348</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3813603670668531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1794284251906522</v>
+        <v>0.1187002973307893</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003382711671292782</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3813603670668531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1794284251906522</v>
+        <v>0.1187002973307893</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.003862015902996063</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1794285766414469</v>
+        <v>0.1187004487815839</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01435585506260395</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1794287918609974</v>
+        <v>0.1187006640011345</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001839019358158112</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4621290720809758</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1794287041789584</v>
+        <v>0.1187005763190954</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.003330201841890812</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4621290720809758</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1794286563523917</v>
+        <v>0.1187005284925287</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.004913421347737312</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1813603670668529</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1794287041789584</v>
+        <v>0.1187005763190954</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.005496572703123093</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1813603670668529</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1794285208437857</v>
+        <v>0.1187003929839227</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.009310539811849594</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.024849806214682</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1794285288148802</v>
+        <v>0.1187004009550172</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.006384532898664474</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1794285367859746</v>
+        <v>0.1187004089261116</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01033354550600052</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.024849806214682</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1794285447570691</v>
+        <v>0.1187004168972061</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01275842078030109</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3813603670668529</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1794285447570691</v>
+        <v>0.1187004168972061</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005488431081175804</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2621290720809758</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1794285846125414</v>
+        <v>0.1187004567526784</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.004341565072536469</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1794286483812972</v>
+        <v>0.1187005205214343</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005196394398808479</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.462129072080976</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1794287599766196</v>
+        <v>0.1187006321167566</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0009682364761829376</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.462129072080976</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1794288078031863</v>
+        <v>0.1187006799433234</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002456792630255222</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.462129072080976</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1794287679477141</v>
+        <v>0.1187006400878511</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003597138449549675</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.179428696207864</v>
+        <v>0.118700568348001</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007797904312610626</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1794288157742808</v>
+        <v>0.1187006879144178</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01356622669845819</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.105618511228805</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1794286563523917</v>
+        <v>0.1187005284925287</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001260601915419102</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.462129072080976</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1794284251906522</v>
+        <v>0.1187002973307893</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.003560446202754974</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3813603670668528</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1794283773640855</v>
+        <v>0.1187002495042225</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.009416690096259117</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.024849806214682</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1794284092484633</v>
+        <v>0.1187002813886004</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.003477610647678375</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.007339701056480408</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01050506718456745</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1794283933062744</v>
+        <v>0.1187002654464114</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.00984455831348896</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1794282737398574</v>
+        <v>0.1187001458799944</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01548256911337376</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1794282338843851</v>
+        <v>0.1187001060245221</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01246476173400879</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1794283773640855</v>
+        <v>0.1187002495042225</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0128315556794405</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1794285128726913</v>
+        <v>0.1187003850128283</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01711519621312618</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1794284969305024</v>
+        <v>0.1187003690706394</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01678978279232979</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01569371297955513</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1794284331617467</v>
+        <v>0.1187003053018837</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.007903640158474445</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1794283295375188</v>
+        <v>0.1187002016776558</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.008172871544957161</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1794282099711017</v>
+        <v>0.1187000821112387</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.01607994362711906</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1794283295375188</v>
+        <v>0.1187002016776558</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01353692077100277</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1794283773640855</v>
+        <v>0.1187002495042225</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01476506888866425</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.179428473017219</v>
+        <v>0.118700345157356</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01343704387545586</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3700000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1794283534508022</v>
+        <v>0.1187002255909392</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.002780353650450706</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1794283614218966</v>
+        <v>0.1187002335620336</v>
       </c>
     </row>
   </sheetData>
